--- a/primary_genes/lung_genes_primary_results.xlsx
+++ b/primary_genes/lung_genes_primary_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/primary genes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/primary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419288F2-B0F7-6A49-AD74-C6E42F519EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF68C278-A2A0-A146-A423-CB7C3FD2F16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13080" yWindow="0" windowWidth="15720" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14520" yWindow="0" windowWidth="14280" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/primary_genes/lung_genes_primary_results.xlsx
+++ b/primary_genes/lung_genes_primary_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/primary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF68C278-A2A0-A146-A423-CB7C3FD2F16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4229B76-DAB7-744B-8ECB-6AADF17B2600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14520" yWindow="0" windowWidth="14280" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39140" yWindow="3280" windowWidth="30780" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1199,8 +1199,9 @@
   <cols>
     <col min="1" max="1" width="14.1640625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">

--- a/primary_genes/lung_genes_primary_results.xlsx
+++ b/primary_genes/lung_genes_primary_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/primary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4229B76-DAB7-744B-8ECB-6AADF17B2600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8385B9D-196A-D74A-8434-F248BCF2F621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39140" yWindow="3280" windowWidth="30780" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
